--- a/DataTables/DetailText/剧情/金钱过低.xlsx
+++ b/DataTables/DetailText/剧情/金钱过低.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F33A8DF0-2B35-45DD-8F5F-AB7F1593639E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0999078-E0FF-49BF-845E-155EC75F515A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
   <si>
     <t>LineIndex</t>
   </si>
@@ -63,31 +63,10 @@
     <t>subtitle</t>
   </si>
   <si>
-    <t>left</t>
-  </si>
-  <si>
-    <t>dim</t>
-  </si>
-  <si>
-    <t>res://Assets/Background/</t>
-  </si>
-  <si>
     <t>dialogue</t>
   </si>
   <si>
-    <t>right</t>
-  </si>
-  <si>
-    <t>hide</t>
-  </si>
-  <si>
     <t>current_scene</t>
-  </si>
-  <si>
-    <t>mid</t>
-  </si>
-  <si>
-    <t>normal</t>
   </si>
   <si>
     <t>PlayOnce</t>
@@ -193,12 +172,28 @@
   <si>
     <t>night</t>
   </si>
+  <si>
+    <t>李言闻</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>mid</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>因经营不善，医馆被迫关闭</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>东璧锕，咱们这医馆已经经营不下去了，我们收拾行李回乡下老家吧…</t>
+    <phoneticPr fontId="4"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -253,6 +248,13 @@
       <color theme="1"/>
       <name val="Noto Sans JP"/>
       <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Microsoft YaHei"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -331,7 +333,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -404,6 +406,15 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -639,77 +650,77 @@
   <sheetData>
     <row r="1" spans="1:20" s="21" customFormat="1" ht="36">
       <c r="A1" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="H1" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="L1" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="N1" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="D1" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="E1" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="F1" s="14" t="s">
+      <c r="O1" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="G1" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="H1" s="14" t="s">
+      <c r="P1" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q1" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="I1" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="J1" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="K1" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="19" t="s">
-        <v>37</v>
-      </c>
-      <c r="M1" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="N1" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="O1" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="P1" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q1" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="R1" s="15" t="s">
-        <v>31</v>
-      </c>
       <c r="S1" s="20" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="T1" s="20" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:20" s="21" customFormat="1" ht="18">
       <c r="A2" s="22"/>
       <c r="B2" s="25" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="C2" s="23" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="D2" s="23"/>
       <c r="E2" s="23" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="F2" s="23">
         <v>0</v>
@@ -720,7 +731,7 @@
       <c r="J2" s="22"/>
       <c r="K2" s="23"/>
       <c r="L2" s="23" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="M2" s="22"/>
       <c r="N2" s="23"/>
@@ -1015,66 +1026,52 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="2" t="s">
         <v>9</v>
       </c>
+      <c r="C2" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2" s="27" t="s">
+        <v>36</v>
+      </c>
       <c r="E2" s="2"/>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="7"/>
+      <c r="G2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H2" s="1"/>
+      <c r="H2" s="26" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>12</v>
+      <c r="B3" s="28" t="s">
+        <v>8</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="2" t="s">
-        <v>13</v>
-      </c>
+      <c r="D3" s="2"/>
       <c r="E3" s="2"/>
-      <c r="F3" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H3" s="1"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="26" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="1">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>12</v>
-      </c>
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
       <c r="C4" s="1"/>
-      <c r="D4" s="7" t="s">
-        <v>16</v>
-      </c>
+      <c r="D4" s="7"/>
       <c r="E4" s="2"/>
-      <c r="F4" s="7" t="s">
-        <v>17</v>
-      </c>
+      <c r="F4" s="7"/>
       <c r="G4" s="2"/>
       <c r="H4" s="1"/>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="1">
-        <v>4</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>12</v>
-      </c>
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
       <c r="C5" s="1"/>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
@@ -1083,9 +1080,7 @@
       <c r="H5" s="1"/>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="1">
-        <v>5</v>
-      </c>
+      <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
       <c r="D6" s="2"/>
